--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_931_Denmark_Baltic_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_931_Denmark_Baltic_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R684ebc6f2ea147e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8f0a7806a60d445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rccbfabae9e3c4ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R173859f27e2e4a63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfa00388fa0d0473e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra50dd5f1de324587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb3423e2ff2df4f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R04de691b0e49475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb4ea6a1264054b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9abe469fbe354f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc59e436cd6184d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R234424152ca8450c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ931CommercialTable" displayName="EEZ931CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ931CommercialTable" displayName="EEZ931CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ931FunctionalTable" displayName="EEZ931FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ931FunctionalTable" displayName="EEZ931FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ931ValidationTable" displayName="EEZ931ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ931ValidationTable" displayName="EEZ931ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5183,7 +5137,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84f67ce27eea494a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42df49f5bf0a4815"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5193,20 +5147,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5214,660 +5158,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.2247596604</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.2247596604</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$68,A2,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>28.9546531749001</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>28.9546531749001</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8754.833578838501</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.13699706570263</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1370.8725038754637</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8754.833578838501</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1414.951062670836</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$68,A3,'Species'!$U$2:$U$68))</x:f>
-        <x:v>12387661.075883856</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.13699706570263</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1370.8725038754637</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>12001760.629235324</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>385900.4466485325</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.03215365299892</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.032153652998920014</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>40.40431014580001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.633675433236259</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>43.02049798178768</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>40.40431014580001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>43.92388529490424</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$68,A4,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1774.7142842638552</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.633675433236259</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>43.02049798178768</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1738.2135430829128</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>36.50074118094244</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0209989971175835</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.020998997117583358</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>9829.620679532001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3269815624289536</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>212.31543235313345</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>9829.620679532001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>246.0836711279411</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$68,A5,'Species'!$U$2:$U$68))</x:f>
-        <x:v>2418909.142614362</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3269815624289536</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>212.31543235313345</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2086980.1644421383</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>331928.97817222355</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1590475002243015</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.1590475002243014</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>29464.1182284632</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.203436905684158</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>159.74854294664385</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>29464.1182284632</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>174.24286330195508</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$68,A6,'Species'!$U$2:$U$68))</x:f>
-        <x:v>5133912.324794756</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.203436905684158</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>159.74854294664385</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4706849.956204645</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>427062.3685901109</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0907320973822738</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09073209738227377</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>15913.975289273698</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0041323561438045</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.095605141559965</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>15913.975289273698</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>11.304204630581413</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$68,A7,'Species'!$U$2:$U$68))</x:f>
-        <x:v>179894.83315596593</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0041323561438045</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.095605141559965</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>160661.21075304976</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>19233.622402916168</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1197154080488034</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1197154080488035</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1825.1798004714</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5882479738993602</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>387.47882481931805</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1825.1798004714</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>693.188307398936</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$68,A8,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1265193.2965874975</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5882479738993602</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>387.47882481931805</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>707218.5241706155</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>557974.772416882</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.788970810784746</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.788970810784746</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>222.38669981370006</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9692286193651825</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>931.5981541588172</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>222.38669981370006</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1404.7701731557156</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$68,A9,'Species'!$U$2:$U$68))</x:f>
-        <x:v>312402.20280481956</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9692286193651825</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>931.5981541588172</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>207175.03905591395</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>105227.16374890562</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5079142942529198</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5079142942529198</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>470.50345896849996</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5817591487816705</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>381.73251074844313</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>470.50345896849996</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>601.8170849925168</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$68,A10,'Species'!$U$2:$U$68))</x:f>
-        <x:v>283157.0201553189</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5817591487816705</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>381.73251074844313</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>179606.46670787258</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>103550.55344744632</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.5765413425557213</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.5765413425557213</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>44.6116565984</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.889951421295324</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>776.1602931204974</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>44.6116565984</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>776.17309604709</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$68,A11,'Species'!$U$2:$U$68))</x:f>
-        <x:v>34626.36762176972</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.889951421295324</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>776.1602931204974</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>34625.79646200512</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.571159764600452</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0000164952094381</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.000016495209438061173</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.006159248599999999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.014395390048066</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1033.7020797446874</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.006159248599999999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1246.4633750883045</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$68,A12,'Species'!$U$2:$U$68))</x:f>
-        <x:v>7.677277797963913</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.014395390048066</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1033.7020797446874</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6.366828087484553</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1.31044971047936</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2058245789697615</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2058245789697615</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35cc52364c0c4b3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a91a544323b4526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5877,20 +5392,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5898,1092 +5403,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>7256.2059290263</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.091583280382873</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1234.7620706521138</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>7256.2059290263</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1237.7053761538282</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$68,A2,'Species'!$U$2:$U$68))</x:f>
-        <x:v>8981045.088835135</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.091583280382873</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1234.7620706521138</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>8959687.858002659</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>21357.23083247617</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0023837025542581</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.002383702554258094</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>411.81066758289995</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.685571727677805</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>484.8101768161067</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>411.81066758289995</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>568.7941834941847</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$68,A3,'Species'!$U$2:$U$68))</x:f>
-        <x:v>234235.51242201068</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.685571727677805</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>484.8101768161067</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>199650.0025656247</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>34585.509856385994</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1732307007860807</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1732307007860808</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3867.1169247925004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2944216497752037</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>196.97978077588618</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3867.1169247925004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>247.96257082449293</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$68,A4,'Species'!$U$2:$U$68))</x:f>
-        <x:v>958900.2543504557</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2944216497752037</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>196.97978077588618</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>761743.8440803458</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>197156.4102701099</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2588224529837022</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2588224529837022</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>380.4604348051</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4387643518553284</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>274.6403550432669</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>380.4604348051</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>329.5566533018629</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$68,A5,'Species'!$U$2:$U$68))</x:f>
-        <x:v>125383.26760814036</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4387643518553284</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>274.6403550432669</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>104489.78889478836</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>20893.478713352</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1999571339395643</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.19995713393956435</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.8399999999999994</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>691.8309709189356</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$68,A6,'Species'!$U$2:$U$68))</x:f>
-        <x:v>2.075492912756809</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.8399999999999994</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>691.8309709189356</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2.0754929127568067</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2.220446049250313e-15</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.0698403427940258e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.0021061658</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.37</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2344.228815319923</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.0021061658</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2344.228815319923</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$68,A7,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4.9373345582013375</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.37</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2344.228815319923</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>4.9373345582013375</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>29.676900383200003</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>2.6133081604240442</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>41.04952729964078</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>29.676900383200003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>42.09542398866223</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$68,A8,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1249.2617043000969</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>2.6133081604240442</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>41.04952729964078</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1218.2227324488883</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>31.038971851208544</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0254788972693143</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.025478897269314266</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1847.7037542374</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.137857309344062</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1373.590597540702</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1847.7037542374</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1923.0997568551397</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$68,A9,'Species'!$U$2:$U$68))</x:f>
-        <x:v>3553318.6405142727</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.137857309344062</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1373.590597540702</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2537988.503861149</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1015330.1366531239</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.400053087359718</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.4000530873597179</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>625.7113350363</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3600820867607646</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>229.13006945993723</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>625.7113350363</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>522.5503330017393</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$68,A10,'Species'!$U$2:$U$68))</x:f>
-        <x:v>326965.6664861815</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3600820867607646</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>229.13006945993723</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>143369.28165873748</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>183596.384827444</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>2.2805838370904254</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>1.2805838370904254</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>16152.2007188408</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.41527723121737</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>260.1819900920739</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>16152.2007188408</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>294.146000760082</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$68,A11,'Species'!$U$2:$U$68))</x:f>
-        <x:v>4751105.244921143</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.41527723121737</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>260.1819900920739</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4202511.727394626</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>548593.5175265176</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1305394376297486</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.13053943762974857</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.2033509354</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.2033509354</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$68,A12,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6.890427610573045</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>6.890427610573045</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>15913.975289273698</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.0041323561438045</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>10.095605141559965</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>15913.975289273698</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>11.304204630581413</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$68,A13,'Species'!$U$2:$U$68))</x:f>
-        <x:v>179894.83315596593</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.0041323561438045</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>10.095605141559965</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>160661.21075304976</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>19233.622402916168</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1197154080488034</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.1197154080488035</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>10.7274097626</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.6900205845544156</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>48.98020343023486</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>10.7274097626</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>48.98224190108726</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$68,A14,'Species'!$U$2:$U$68))</x:f>
-        <x:v>525.4525799637582</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.6900205845544156</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>48.98020343023486</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>525.4307124516355</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0.021867512122753396</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0000416182602283</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.00004161826022830031</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>4.9746522812</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3100000000000005</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>204.17379446695315</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>4.9746522812</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$68,A15,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1015.6936324062874</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3100000000000005</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>204.17379446695315</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1015.6936324062884</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>-1.0231815394945443e-12</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>-1.0073722103293256e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>37.8992777137</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0800206948471662</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>120.23217258623554</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>37.8992777137</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>120.23409220565186</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$68,A16,'Species'!$U$2:$U$68))</x:f>
-        <x:v>4556.7852511566125</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0800206948471662</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>120.23217258623554</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4556.712498967248</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0.07275218936410965</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0000159659380268</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.00001596593802672398</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>14060.4298561611</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.010001598526238</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>102.32967587658828</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>14060.4298561611</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>102.32972276808746</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$68,A17,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1438799.8891811052</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.010001598526238</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>102.32967587658828</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1438799.2298664702</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0.6593146349769086</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0000004582394968</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>4.5823949672123276e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4.2582061939</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4.2582061939</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$68,A18,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>548.5632220308601</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>548.5632220308601</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>5962.5037547395</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.348099031611761</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>222.8943354409823</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>5962.5037547395</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>244.86506815251354</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$68,A19,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1460008.8882639057</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.348099031611761</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>222.8943354409823</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1329008.3119770228</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>131000.57628688286</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.098570170785469</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0985701707854689</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.0010530828</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.8000000000000003</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>630.9573444801937</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.0010530828</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$68,A20,'Species'!$U$2:$U$68))</x:f>
-        <x:v>0.6644503270057661</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.8000000000000003</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>630.9573444801937</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>0.6644503270057669</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>-7.771561172376096e-16</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>-1.1696225972823767e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cc81ee706f24477"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac87cb156fca4c25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7158,7 +5954,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7257,7 +6053,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>22017567.609833583</x:v>
+        <x:v>20086651.322055914</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7271,7 +6067,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>22017567.609833587</x:v>
+        <x:v>19845788.949558187</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7285,7 +6081,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1930916.2877776697</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7299,7 +6095,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-2171778.660275396</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7310,9 +6106,9 @@
         <x:v>EEZ_931</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7324,47 +6120,19 @@
         <x:v>EEZ_931</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_931</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_931</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc36dcee5bf2444d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9a6bc292eb34ad5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7411,7 +6179,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
